--- a/TVV.xlsx
+++ b/TVV.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="93">
   <si>
     <t>3607/2016</t>
   </si>
@@ -309,15 +309,20 @@
   </si>
   <si>
     <t>4907/2026</t>
+  </si>
+  <si>
+    <t>https://www3.bcb.gov.br/CALCIDADAO/publico/exibirFormCorrecaoValores.do?method=exibirFormCorrecaoValores&amp;aba=1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000%"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;????_-;_-@_-"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -428,13 +433,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -496,6 +502,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -505,12 +513,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="3" builtinId="5"/>
+    <cellStyle name="Vírgula" xfId="4" builtinId="3"/>
   </cellStyles>
   <dxfs count="45">
     <dxf>
@@ -1864,7 +1876,7 @@
         <v>136.15199999999999</v>
       </c>
       <c r="D4" s="13">
-        <v>108.93647999999999</v>
+        <v>108.93648</v>
       </c>
       <c r="E4" s="13">
         <v>81.67631999999999</v>
@@ -1921,37 +1933,37 @@
         <v>0</v>
       </c>
       <c r="W4" s="13">
-        <v>0</v>
+        <v>62.922232040193691</v>
       </c>
       <c r="X4" s="13">
-        <v>0</v>
+        <v>139.82219560746478</v>
       </c>
       <c r="Y4" s="13">
         <v>0</v>
       </c>
       <c r="Z4" s="13">
-        <v>0</v>
+        <v>251.67895475262128</v>
       </c>
       <c r="AA4" s="13">
-        <v>0</v>
+        <v>349.54800896254693</v>
       </c>
       <c r="AB4" s="13">
-        <v>0</v>
+        <v>489.37519127408848</v>
       </c>
       <c r="AC4" s="13">
         <v>0</v>
       </c>
       <c r="AD4" s="13">
-        <v>0</v>
+        <v>104.86540002957942</v>
       </c>
       <c r="AE4" s="13">
         <v>0</v>
       </c>
       <c r="AF4" s="13">
-        <v>0</v>
+        <v>230.6998907018133</v>
       </c>
       <c r="AG4" s="13">
-        <v>0</v>
+        <v>321.57758579616183</v>
       </c>
       <c r="AH4" s="13">
         <v>0</v>
@@ -1960,73 +1972,157 @@
         <v>0</v>
       </c>
       <c r="AJ4" s="13">
-        <v>0</v>
+        <v>94.373374652137059</v>
       </c>
       <c r="AK4" s="13">
         <v>0</v>
       </c>
       <c r="AL4" s="13">
-        <v>0</v>
+        <v>202.734454239505</v>
       </c>
       <c r="AM4" s="13">
-        <v>0</v>
+        <v>265.6566862796987</v>
       </c>
       <c r="AN4" s="13">
         <v>0</v>
       </c>
-      <c r="AO4" s="13"/>
-      <c r="AP4" s="13"/>
-      <c r="AQ4" s="18"/>
+      <c r="AO4" s="13">
+        <v>1.236702611029326</v>
+      </c>
+      <c r="AP4" s="13">
+        <v>55.796231914544869</v>
+      </c>
+      <c r="AQ4" s="18">
+        <v>1.2965430599500998</v>
+      </c>
     </row>
     <row r="5" spans="1:43" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>1982</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="C5" s="4">
+        <v>2057.1799999999998</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1646.04</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1234.1600000000001</v>
+      </c>
+      <c r="F5" s="4">
+        <v>986.51</v>
+      </c>
+      <c r="G5" s="4">
+        <v>877.10705670590517</v>
+      </c>
+      <c r="H5" s="4">
+        <v>701.87741515028426</v>
+      </c>
       <c r="I5" s="4">
-        <v>683.38</v>
-      </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
+        <v>613.18388932869777</v>
+      </c>
+      <c r="J5" s="4">
+        <v>525.68892466686248</v>
+      </c>
+      <c r="K5" s="4">
+        <v>437.95424777307699</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>349.2607219514905</v>
+      </c>
+      <c r="N5" s="4">
+        <v>298.2020165460907</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4">
+        <v>0</v>
+      </c>
+      <c r="U5" s="4">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4">
+        <v>0</v>
+      </c>
       <c r="W5" s="4">
-        <v>1094.97</v>
-      </c>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
-      <c r="AE5" s="4"/>
-      <c r="AF5" s="4"/>
-      <c r="AG5" s="4"/>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
-      <c r="AJ5" s="4"/>
-      <c r="AK5" s="4"/>
-      <c r="AL5" s="4"/>
-      <c r="AM5" s="4"/>
-      <c r="AN5" s="4"/>
-      <c r="AO5" s="4"/>
-      <c r="AP5" s="4"/>
-      <c r="AQ5" s="18"/>
+        <v>950.73560804076317</v>
+      </c>
+      <c r="X5" s="4">
+        <v>2112.6704480785352</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>3802.7917370278424</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>5281.5630988449311</v>
+      </c>
+      <c r="AB5" s="4">
+        <v>7394.3088944910714</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="4">
+        <v>1584.4839991670003</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="4">
+        <v>3485.8045201133159</v>
+      </c>
+      <c r="AG5" s="4">
+        <v>4858.9385921480971</v>
+      </c>
+      <c r="AH5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="4">
+        <v>1425.9527169259345</v>
+      </c>
+      <c r="AK5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="4">
+        <v>3063.2553609840879</v>
+      </c>
+      <c r="AM5" s="4">
+        <v>4013.9909690248514</v>
+      </c>
+      <c r="AN5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="4">
+        <v>18.686196766057162</v>
+      </c>
+      <c r="AP5" s="4">
+        <v>843.0639339331193</v>
+      </c>
+      <c r="AQ5" s="18">
+        <v>19.590367577317991</v>
+      </c>
     </row>
     <row r="6" spans="1:43" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
@@ -2067,7 +2163,7 @@
         <v>1684.9016954520282</v>
       </c>
       <c r="N6" s="13">
-        <v>0</v>
+        <v>1581.8039284229085</v>
       </c>
       <c r="O6" s="13">
         <v>0</v>
@@ -7447,20 +7543,20 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="37"/>
+      <c r="B1" s="39"/>
       <c r="C1" s="8"/>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="37"/>
+      <c r="E1" s="39"/>
       <c r="F1" s="8"/>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="37"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
@@ -7640,21 +7736,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
@@ -7668,26 +7764,41 @@
       <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="DQUGja0DnPXWQ+h+EKUW5ebZur65T0vwyWmaGyxWbM73GXV+aEIqHEdhNSYtU3fkdJtsoumDnuDZri4V/gXyTQ==" saltValue="s7PCd7LbdlozeCrYi6r4wQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="2">
+  <sheetProtection algorithmName="SHA-512" hashValue="lIgT3Z4dXwdT1tSkrLuDpWiG/ELaT0EZqw+QGVlAMAflocEwK20uRl3WtIqQgqQfFOZcLM40mrJmK/Nk7sSh4A==" saltValue="ObTpSljlwEmm8YwASsBh+Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A5:I5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1"/>
+    <hyperlink ref="A5" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7695,364 +7806,575 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AP4"/>
+  <dimension ref="A1:AP14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="10" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="21" width="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="7" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="7" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="7" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="2" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="5" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="42" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>2020</v>
-      </c>
-      <c r="B1">
-        <v>281.72000000000003</v>
-      </c>
-      <c r="C1">
-        <v>225.4</v>
-      </c>
-      <c r="D1">
-        <v>169</v>
-      </c>
-      <c r="E1">
-        <v>135.1</v>
-      </c>
-      <c r="F1">
-        <v>112.65</v>
-      </c>
-      <c r="G1">
-        <v>90.15</v>
-      </c>
-      <c r="H1">
-        <v>78.75</v>
-      </c>
-      <c r="I1">
-        <v>67.510000000000005</v>
-      </c>
-      <c r="J1">
-        <v>56.26</v>
-      </c>
-      <c r="K1">
-        <v>0</v>
-      </c>
-      <c r="L1">
-        <v>51.95</v>
-      </c>
-      <c r="M1">
-        <v>0</v>
-      </c>
-      <c r="N1">
-        <v>0</v>
-      </c>
-      <c r="O1">
-        <v>0</v>
-      </c>
-      <c r="P1">
-        <v>0</v>
-      </c>
-      <c r="Q1">
-        <v>0</v>
-      </c>
-      <c r="R1">
-        <v>0</v>
-      </c>
-      <c r="S1">
-        <v>0</v>
-      </c>
-      <c r="T1">
-        <v>0</v>
-      </c>
-      <c r="U1">
-        <v>0</v>
-      </c>
-      <c r="V1">
-        <v>126.18</v>
-      </c>
-      <c r="W1">
-        <v>280.39</v>
-      </c>
-      <c r="X1">
-        <v>0</v>
-      </c>
-      <c r="Y1">
-        <v>504.7</v>
-      </c>
-      <c r="Z1">
-        <v>700.96</v>
-      </c>
-      <c r="AA1">
-        <v>981.36</v>
-      </c>
-      <c r="AB1">
-        <v>0</v>
-      </c>
-      <c r="AC1">
-        <v>210.29</v>
-      </c>
-      <c r="AD1">
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <v>462.63</v>
-      </c>
-      <c r="AF1">
-        <v>644.87</v>
-      </c>
-      <c r="AG1">
-        <v>0</v>
-      </c>
-      <c r="AH1">
-        <v>0</v>
-      </c>
-      <c r="AI1">
-        <v>189.25</v>
-      </c>
-      <c r="AJ1">
-        <v>0</v>
-      </c>
-      <c r="AK1">
-        <v>406.55</v>
-      </c>
-      <c r="AL1">
-        <v>532.73</v>
-      </c>
-      <c r="AM1">
-        <v>0</v>
-      </c>
-      <c r="AN1">
-        <v>2.48</v>
-      </c>
-      <c r="AO1">
-        <v>111.89</v>
-      </c>
-      <c r="AP1">
-        <v>2.6</v>
+        <v>1977</v>
+      </c>
+      <c r="B1" s="37">
+        <v>136.15199999999999</v>
+      </c>
+      <c r="C1" s="37">
+        <v>108.93648</v>
+      </c>
+      <c r="D1" s="37">
+        <v>81.67631999999999</v>
+      </c>
+      <c r="E1" s="37">
+        <v>65.293440000000004</v>
+      </c>
+      <c r="F1" s="37">
+        <v>54.445920000000001</v>
+      </c>
+      <c r="G1" s="37">
+        <v>43.568640000000002</v>
+      </c>
+      <c r="H1" s="37">
+        <v>38.063040000000001</v>
+      </c>
+      <c r="I1" s="37">
+        <v>32.631839999999997</v>
+      </c>
+      <c r="J1" s="37">
+        <v>27.185759999999998</v>
+      </c>
+      <c r="K1" s="37">
+        <v>0</v>
+      </c>
+      <c r="L1" s="37">
+        <v>21.680160000000001</v>
+      </c>
+      <c r="M1" s="37">
+        <v>18.510719999999999</v>
+      </c>
+      <c r="N1" s="37">
+        <v>0</v>
+      </c>
+      <c r="O1" s="37">
+        <v>0</v>
+      </c>
+      <c r="P1" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="37">
+        <v>0</v>
+      </c>
+      <c r="R1" s="37">
+        <v>0</v>
+      </c>
+      <c r="S1" s="37">
+        <v>0</v>
+      </c>
+      <c r="T1" s="37">
+        <v>0</v>
+      </c>
+      <c r="U1" s="37">
+        <v>0</v>
+      </c>
+      <c r="V1" s="37">
+        <f>V2*$A$14</f>
+        <v>62.922232040193691</v>
+      </c>
+      <c r="W1" s="37">
+        <f t="shared" ref="W1:AP1" si="0">W2*$A$14</f>
+        <v>139.82219560746478</v>
+      </c>
+      <c r="X1" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y1" s="37">
+        <f t="shared" si="0"/>
+        <v>251.67895475262128</v>
+      </c>
+      <c r="Z1" s="37">
+        <f t="shared" si="0"/>
+        <v>349.54800896254693</v>
+      </c>
+      <c r="AA1" s="37">
+        <f t="shared" si="0"/>
+        <v>489.37519127408848</v>
+      </c>
+      <c r="AB1" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC1" s="37">
+        <f t="shared" si="0"/>
+        <v>104.86540002957942</v>
+      </c>
+      <c r="AD1" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE1" s="37">
+        <f t="shared" si="0"/>
+        <v>230.6998907018133</v>
+      </c>
+      <c r="AF1" s="37">
+        <f t="shared" si="0"/>
+        <v>321.57758579616183</v>
+      </c>
+      <c r="AG1" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH1" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI1" s="37">
+        <f t="shared" si="0"/>
+        <v>94.373374652137059</v>
+      </c>
+      <c r="AJ1" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK1" s="37">
+        <f t="shared" si="0"/>
+        <v>202.734454239505</v>
+      </c>
+      <c r="AL1" s="37">
+        <f t="shared" si="0"/>
+        <v>265.6566862796987</v>
+      </c>
+      <c r="AM1" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN1" s="37">
+        <f t="shared" si="0"/>
+        <v>1.236702611029326</v>
+      </c>
+      <c r="AO1" s="37">
+        <f t="shared" si="0"/>
+        <v>55.796231914544869</v>
+      </c>
+      <c r="AP1" s="37">
+        <f t="shared" si="0"/>
+        <v>1.2965430599500998</v>
       </c>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1987</v>
-      </c>
-      <c r="B2" s="31">
-        <v>453.19</v>
+        <v>1982</v>
+      </c>
+      <c r="B2" s="37">
+        <v>2057.1799999999998</v>
       </c>
       <c r="C2" s="31">
-        <v>362.59</v>
+        <v>1646.04</v>
       </c>
       <c r="D2" s="31">
-        <v>271.86</v>
-      </c>
-      <c r="E2" s="31">
-        <v>217.33</v>
-      </c>
-      <c r="F2" s="31">
-        <v>181.22</v>
-      </c>
-      <c r="G2" s="31">
-        <v>145.02000000000001</v>
-      </c>
-      <c r="H2" s="31">
-        <v>126.68</v>
-      </c>
-      <c r="I2" s="31">
-        <v>108.6</v>
-      </c>
-      <c r="J2" s="31">
-        <v>90.5</v>
-      </c>
-      <c r="K2">
-        <f>K1+K1*$A$4</f>
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <f t="shared" ref="L2:AP2" si="0">L1+L1*$A$4</f>
-        <v>135.51933712758125</v>
-      </c>
-      <c r="M2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <f t="shared" si="0"/>
-        <v>329.15938322922432</v>
-      </c>
-      <c r="W2">
-        <f t="shared" si="0"/>
-        <v>731.43920957078933</v>
-      </c>
-      <c r="X2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <f t="shared" si="0"/>
-        <v>1316.5853599285902</v>
-      </c>
-      <c r="Z2">
-        <f t="shared" si="0"/>
-        <v>1828.5588941857432</v>
-      </c>
-      <c r="AA2">
-        <f t="shared" si="0"/>
-        <v>2560.0241902506859</v>
-      </c>
-      <c r="AB2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <f t="shared" si="0"/>
-        <v>548.57288555455364</v>
-      </c>
-      <c r="AD2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <f t="shared" si="0"/>
-        <v>1206.8394790246953</v>
-      </c>
-      <c r="AF2">
-        <f t="shared" si="0"/>
-        <v>1682.2397484786011</v>
-      </c>
-      <c r="AG2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <f t="shared" si="0"/>
-        <v>493.68690185552941</v>
-      </c>
-      <c r="AJ2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <f t="shared" si="0"/>
-        <v>1060.5464198117068</v>
-      </c>
-      <c r="AL2">
-        <f t="shared" si="0"/>
-        <v>1389.705803040931</v>
-      </c>
-      <c r="AM2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <f t="shared" si="0"/>
-        <v>6.4694505500751012</v>
-      </c>
-      <c r="AO2">
-        <f t="shared" si="0"/>
-        <v>291.88178308383186</v>
-      </c>
-      <c r="AP2">
-        <f t="shared" si="0"/>
-        <v>6.7824884799174452</v>
+        <v>1234.1600000000001</v>
+      </c>
+      <c r="E2">
+        <v>986.51</v>
+      </c>
+      <c r="F2" s="37">
+        <f t="shared" ref="F2:J2" si="1">F1+F1*$A$5</f>
+        <v>877.10705670590517</v>
+      </c>
+      <c r="G2" s="37">
+        <f t="shared" si="1"/>
+        <v>701.87741515028426</v>
+      </c>
+      <c r="H2" s="37">
+        <f t="shared" si="1"/>
+        <v>613.18388932869777</v>
+      </c>
+      <c r="I2" s="37">
+        <f t="shared" si="1"/>
+        <v>525.68892466686248</v>
+      </c>
+      <c r="J2" s="37">
+        <f t="shared" si="1"/>
+        <v>437.95424777307699</v>
+      </c>
+      <c r="K2" s="37">
+        <f t="shared" ref="K2:U2" si="2">K1+K1*$A$5</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="37">
+        <f t="shared" si="2"/>
+        <v>349.2607219514905</v>
+      </c>
+      <c r="M2" s="37">
+        <f t="shared" si="2"/>
+        <v>298.2020165460907</v>
+      </c>
+      <c r="N2" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O2" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P2" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R2" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S2" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T2" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U2" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V2" s="37">
+        <f>V3*$A$11</f>
+        <v>950.73560804076317</v>
+      </c>
+      <c r="W2" s="37">
+        <f t="shared" ref="W2:AP2" si="3">W3*$A$11</f>
+        <v>2112.6704480785352</v>
+      </c>
+      <c r="X2" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y2" s="37">
+        <f t="shared" si="3"/>
+        <v>3802.7917370278424</v>
+      </c>
+      <c r="Z2" s="37">
+        <f t="shared" si="3"/>
+        <v>5281.5630988449311</v>
+      </c>
+      <c r="AA2" s="37">
+        <f t="shared" si="3"/>
+        <v>7394.3088944910714</v>
+      </c>
+      <c r="AB2" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC2" s="37">
+        <f t="shared" si="3"/>
+        <v>1584.4839991670003</v>
+      </c>
+      <c r="AD2" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE2" s="37">
+        <f t="shared" si="3"/>
+        <v>3485.8045201133159</v>
+      </c>
+      <c r="AF2" s="37">
+        <f t="shared" si="3"/>
+        <v>4858.9385921480971</v>
+      </c>
+      <c r="AG2" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH2" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI2" s="37">
+        <f t="shared" si="3"/>
+        <v>1425.9527169259345</v>
+      </c>
+      <c r="AJ2" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK2" s="37">
+        <f t="shared" si="3"/>
+        <v>3063.2553609840879</v>
+      </c>
+      <c r="AL2" s="37">
+        <f t="shared" si="3"/>
+        <v>4013.9909690248514</v>
+      </c>
+      <c r="AM2" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN2" s="37">
+        <f t="shared" si="3"/>
+        <v>18.686196766057162</v>
+      </c>
+      <c r="AO2" s="37">
+        <f t="shared" si="3"/>
+        <v>843.0639339331193</v>
+      </c>
+      <c r="AP2" s="37">
+        <f t="shared" si="3"/>
+        <v>19.590367577317991</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="32">
-        <f>B2/B1</f>
-        <v>1.6086539826778359</v>
-      </c>
-      <c r="C3" s="32">
-        <f t="shared" ref="C3:J3" si="1">C2/C1</f>
-        <v>1.608651286601597</v>
-      </c>
-      <c r="D3" s="32">
-        <f t="shared" si="1"/>
-        <v>1.6086390532544379</v>
-      </c>
-      <c r="E3" s="32">
-        <f t="shared" si="1"/>
-        <v>1.6086602516654331</v>
-      </c>
-      <c r="F3" s="32">
-        <f t="shared" si="1"/>
-        <v>1.6086995117620948</v>
-      </c>
-      <c r="G3" s="32">
-        <f t="shared" si="1"/>
-        <v>1.6086522462562396</v>
-      </c>
-      <c r="H3" s="32">
-        <f t="shared" si="1"/>
-        <v>1.6086349206349206</v>
-      </c>
-      <c r="I3" s="32">
-        <f t="shared" si="1"/>
-        <v>1.6086505702858833</v>
-      </c>
-      <c r="J3" s="32">
-        <f t="shared" si="1"/>
-        <v>1.6086029150373267</v>
+      <c r="A3">
+        <v>1983</v>
+      </c>
+      <c r="B3" s="37">
+        <v>8855.34</v>
+      </c>
+      <c r="C3" s="31">
+        <v>7085.03</v>
+      </c>
+      <c r="D3" s="31">
+        <v>5312.2</v>
+      </c>
+      <c r="E3" s="37">
+        <v>4246.62</v>
+      </c>
+      <c r="F3" s="37">
+        <v>3540.94</v>
+      </c>
+      <c r="G3" s="37">
+        <v>2833.7</v>
+      </c>
+      <c r="H3" s="37">
+        <v>2475.36</v>
+      </c>
+      <c r="I3" s="37">
+        <v>2122.0500000000002</v>
+      </c>
+      <c r="J3" s="37">
+        <v>1768.43</v>
+      </c>
+      <c r="K3" s="37">
+        <v>0</v>
+      </c>
+      <c r="L3" s="37">
+        <v>1684.9016954520282</v>
+      </c>
+      <c r="M3" s="37">
+        <f>M2+M2*A8</f>
+        <v>1581.8039284229085</v>
+      </c>
+      <c r="N3" s="37">
+        <v>0</v>
+      </c>
+      <c r="O3" s="37">
+        <v>0</v>
+      </c>
+      <c r="P3" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="37">
+        <v>0</v>
+      </c>
+      <c r="R3" s="37">
+        <v>0</v>
+      </c>
+      <c r="S3" s="37">
+        <v>0</v>
+      </c>
+      <c r="T3" s="37">
+        <v>0</v>
+      </c>
+      <c r="U3" s="37">
+        <v>0</v>
+      </c>
+      <c r="V3" s="37">
+        <v>4092.413781176841</v>
+      </c>
+      <c r="W3" s="37">
+        <v>9093.928515645699</v>
+      </c>
+      <c r="X3" s="37">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="37">
+        <v>16369.006461879471</v>
+      </c>
+      <c r="Z3" s="37">
+        <v>22734.334791993333</v>
+      </c>
+      <c r="AA3" s="37">
+        <v>31828.587639052981</v>
+      </c>
+      <c r="AB3" s="37">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="37">
+        <v>6820.3653038807888</v>
+      </c>
+      <c r="AD3" s="37">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="37">
+        <v>15004.544203406576</v>
+      </c>
+      <c r="AF3" s="37">
+        <v>20915.159891167455</v>
+      </c>
+      <c r="AG3" s="37">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="37">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="37">
+        <v>6137.9720089373686</v>
+      </c>
+      <c r="AJ3" s="37">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="37">
+        <v>13185.693633994648</v>
+      </c>
+      <c r="AL3" s="37">
+        <v>17278.107415171489</v>
+      </c>
+      <c r="AM3" s="37">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>80.434190658730117</v>
+      </c>
+      <c r="AO3">
+        <v>3628.9441906473035</v>
+      </c>
+      <c r="AP3">
+        <v>84.326167626088022</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A4" s="33">
-        <f>AVERAGE(B3:J3)</f>
-        <v>1.6086494153528634</v>
+      <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="32">
+        <f>B2/B1</f>
+        <v>15.109436512133499</v>
+      </c>
+      <c r="C4" s="32">
+        <f t="shared" ref="C4:E4" si="4">C2/C1</f>
+        <v>15.110089843182008</v>
+      </c>
+      <c r="D4" s="32">
+        <f t="shared" si="4"/>
+        <v>15.110377157051152</v>
+      </c>
+      <c r="E4" s="32">
+        <f t="shared" si="4"/>
+        <v>15.108868517266052</v>
+      </c>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+    </row>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A5" s="33">
+        <f>AVERAGE(B4:E4)</f>
+        <v>15.109693007408179</v>
+      </c>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+    </row>
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="B7" s="32">
+        <f>B3/B2</f>
+        <v>4.3046014446961376</v>
+      </c>
+      <c r="C7" s="32">
+        <f t="shared" ref="C7:E7" si="5">C3/C2</f>
+        <v>4.3042878666375053</v>
+      </c>
+      <c r="D7" s="32">
+        <f t="shared" si="5"/>
+        <v>4.3043041420885455</v>
+      </c>
+      <c r="E7" s="32">
+        <f t="shared" si="5"/>
+        <v>4.3046902717661251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A8" s="33">
+        <f>AVERAGE(B7:E7)</f>
+        <v>4.3044709312970788</v>
+      </c>
+    </row>
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="B10" s="32">
+        <f>B2/B3</f>
+        <v>0.23230954429756506</v>
+      </c>
+      <c r="C10" s="32">
+        <f t="shared" ref="C10:E10" si="6">C2/C3</f>
+        <v>0.23232646862469178</v>
+      </c>
+      <c r="D10" s="32">
+        <f t="shared" si="6"/>
+        <v>0.23232559015097326</v>
+      </c>
+      <c r="E10" s="32">
+        <f t="shared" si="6"/>
+        <v>0.23230475060165498</v>
+      </c>
+    </row>
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A11" s="33">
+        <f>AVERAGE(B10:E10)</f>
+        <v>0.2323165884187213</v>
+      </c>
+    </row>
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="B13" s="32">
+        <f>B1/B2</f>
+        <v>6.6183805014631683E-2</v>
+      </c>
+      <c r="C13" s="32">
+        <f t="shared" ref="C13:E13" si="7">C1/C2</f>
+        <v>6.6180943354960997E-2</v>
+      </c>
+      <c r="D13" s="32">
+        <f t="shared" si="7"/>
+        <v>6.6179684967913391E-2</v>
+      </c>
+      <c r="E13" s="32">
+        <f t="shared" si="7"/>
+        <v>6.6186293093835849E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A14" s="33">
+        <f>AVERAGE(B13:E13)</f>
+        <v>6.618268160783547E-2</v>
       </c>
     </row>
   </sheetData>

--- a/TVV.xlsx
+++ b/TVV.xlsx
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="Q5" s="4">
-        <v>0</v>
+        <v>170.51856587234201</v>
       </c>
       <c r="R5" s="4">
-        <v>0</v>
+        <v>85.259282936171005</v>
       </c>
       <c r="S5" s="4">
         <v>0</v>
@@ -2061,67 +2061,67 @@
         <v>0</v>
       </c>
       <c r="W5" s="4">
-        <v>950.73560804076317</v>
+        <v>659.22447642386703</v>
       </c>
       <c r="X5" s="4">
-        <v>2112.6704480785352</v>
+        <v>1393.8187647390264</v>
       </c>
       <c r="Y5" s="4">
-        <v>0</v>
+        <v>2194.5739792695554</v>
       </c>
       <c r="Z5" s="4">
-        <v>3802.7917370278424</v>
+        <v>3059.1035096599735</v>
       </c>
       <c r="AA5" s="4">
-        <v>5281.5630988449311</v>
+        <v>3947.5055297949793</v>
       </c>
       <c r="AB5" s="4">
-        <v>7394.3088944910714</v>
+        <v>5253.6774889295284</v>
       </c>
       <c r="AC5" s="4">
-        <v>0</v>
+        <v>864.52953039041802</v>
       </c>
       <c r="AD5" s="4">
-        <v>1584.4839991670003</v>
+        <v>1307.8779841210726</v>
       </c>
       <c r="AE5" s="4">
-        <v>0</v>
+        <v>2615.7550559293181</v>
       </c>
       <c r="AF5" s="4">
-        <v>3485.8045201133159</v>
+        <v>3502.451963390628</v>
       </c>
       <c r="AG5" s="4">
-        <v>4858.9385921480971</v>
+        <v>4832.4964122697647</v>
       </c>
       <c r="AH5" s="4">
-        <v>0</v>
+        <v>5697.0259426601833</v>
       </c>
       <c r="AI5" s="4">
-        <v>0</v>
+        <v>659.22447642386703</v>
       </c>
       <c r="AJ5" s="4">
-        <v>1425.9527169259345</v>
+        <v>1393.8187647390264</v>
       </c>
       <c r="AK5" s="4">
-        <v>0</v>
+        <v>2194.5739792695554</v>
       </c>
       <c r="AL5" s="4">
-        <v>3063.2553609840879</v>
+        <v>3059.1035096599735</v>
       </c>
       <c r="AM5" s="4">
-        <v>4013.9909690248514</v>
+        <v>3947.5055297949793</v>
       </c>
       <c r="AN5" s="4">
-        <v>0</v>
+        <v>5253.6774889295284</v>
       </c>
       <c r="AO5" s="4">
-        <v>18.686196766057162</v>
+        <v>18.795468862231637</v>
       </c>
       <c r="AP5" s="4">
-        <v>843.0639339331193</v>
+        <v>847.12716321504331</v>
       </c>
       <c r="AQ5" s="18">
-        <v>19.590367577317991</v>
+        <v>19.682236930093453</v>
       </c>
     </row>
     <row r="6" spans="1:43" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -2172,10 +2172,10 @@
         <v>0</v>
       </c>
       <c r="Q6" s="13">
-        <v>0</v>
+        <v>707.95269417989414</v>
       </c>
       <c r="R6" s="13">
-        <v>0</v>
+        <v>353.97634708994707</v>
       </c>
       <c r="S6" s="13">
         <v>0</v>
@@ -2190,67 +2190,67 @@
         <v>0</v>
       </c>
       <c r="W6" s="13">
-        <v>4092.413781176841</v>
+        <v>2736.9438733316551</v>
       </c>
       <c r="X6" s="13">
-        <v>9093.928515645699</v>
+        <v>5786.8053525281093</v>
       </c>
       <c r="Y6" s="13">
-        <v>0</v>
+        <v>9111.3513256035094</v>
       </c>
       <c r="Z6" s="13">
-        <v>16369.006461879471</v>
+        <v>12700.673151686546</v>
       </c>
       <c r="AA6" s="13">
-        <v>22734.334791993333</v>
+        <v>16389.107900429954</v>
       </c>
       <c r="AB6" s="13">
-        <v>31828.587639052981</v>
+        <v>21812.024477290055</v>
       </c>
       <c r="AC6" s="13">
-        <v>0</v>
+        <v>3589.3218260830358</v>
       </c>
       <c r="AD6" s="13">
-        <v>6820.3653038807888</v>
+        <v>5429.9995884921118</v>
       </c>
       <c r="AE6" s="13">
-        <v>0</v>
+        <v>10859.995389277468</v>
       </c>
       <c r="AF6" s="13">
-        <v>15004.544203406576</v>
+        <v>14541.350914095621</v>
       </c>
       <c r="AG6" s="13">
-        <v>20915.159891167455</v>
+        <v>20063.380413616094</v>
       </c>
       <c r="AH6" s="13">
-        <v>0</v>
+        <v>23652.702239699131</v>
       </c>
       <c r="AI6" s="13">
-        <v>0</v>
+        <v>2736.9438733316551</v>
       </c>
       <c r="AJ6" s="13">
-        <v>6137.9720089373686</v>
+        <v>5786.8053525281093</v>
       </c>
       <c r="AK6" s="13">
-        <v>0</v>
+        <v>9111.3513256035094</v>
       </c>
       <c r="AL6" s="13">
-        <v>13185.693633994648</v>
+        <v>12700.673151686546</v>
       </c>
       <c r="AM6" s="13">
-        <v>17278.107415171489</v>
+        <v>16389.107900429954</v>
       </c>
       <c r="AN6" s="13">
-        <v>0</v>
+        <v>21812.024477290055</v>
       </c>
       <c r="AO6" s="13">
-        <v>80.434190658730117</v>
+        <v>78.034334568312659</v>
       </c>
       <c r="AP6" s="13">
-        <v>3628.9441906473035</v>
+        <v>3517.0713197297418</v>
       </c>
       <c r="AQ6" s="18">
-        <v>84.326167626088022</v>
+        <v>81.715985534257698</v>
       </c>
     </row>
     <row r="7" spans="1:43" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -7809,23 +7809,26 @@
   <dimension ref="A1:AP14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="42" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="33" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="39" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -7833,40 +7836,40 @@
         <v>1977</v>
       </c>
       <c r="B1" s="37">
-        <v>136.15199999999999</v>
+        <v>2057.1799999999998</v>
       </c>
       <c r="C1" s="37">
-        <v>108.93648</v>
+        <v>1646.04</v>
       </c>
       <c r="D1" s="37">
-        <v>81.67631999999999</v>
+        <v>1234.1600000000001</v>
       </c>
       <c r="E1" s="37">
-        <v>65.293440000000004</v>
+        <v>986.51</v>
       </c>
       <c r="F1" s="37">
-        <v>54.445920000000001</v>
+        <v>877.10705670590517</v>
       </c>
       <c r="G1" s="37">
-        <v>43.568640000000002</v>
+        <v>701.87741515028426</v>
       </c>
       <c r="H1" s="37">
-        <v>38.063040000000001</v>
+        <v>613.18388932869777</v>
       </c>
       <c r="I1" s="37">
-        <v>32.631839999999997</v>
+        <v>525.68892466686248</v>
       </c>
       <c r="J1" s="37">
-        <v>27.185759999999998</v>
+        <v>437.95424777307699</v>
       </c>
       <c r="K1" s="37">
         <v>0</v>
       </c>
       <c r="L1" s="37">
-        <v>21.680160000000001</v>
+        <v>349.2607219514905</v>
       </c>
       <c r="M1" s="37">
-        <v>18.510719999999999</v>
+        <v>298.2020165460907</v>
       </c>
       <c r="N1" s="37">
         <v>0</v>
@@ -7875,106 +7878,112 @@
         <v>0</v>
       </c>
       <c r="P1" s="37">
-        <v>0</v>
+        <f>P2*$A$11</f>
+        <v>170.51856587234201</v>
       </c>
       <c r="Q1" s="37">
-        <v>0</v>
+        <f t="shared" ref="Q1:AP1" si="0">Q2*$A$11</f>
+        <v>85.259282936171005</v>
       </c>
       <c r="R1" s="37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S1" s="37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T1" s="37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U1" s="37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V1" s="37">
-        <f>V2*$A$14</f>
-        <v>62.922232040193691</v>
+        <f t="shared" si="0"/>
+        <v>659.22447642386703</v>
       </c>
       <c r="W1" s="37">
-        <f t="shared" ref="W1:AP1" si="0">W2*$A$14</f>
-        <v>139.82219560746478</v>
+        <f t="shared" si="0"/>
+        <v>1393.8187647390264</v>
       </c>
       <c r="X1" s="37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2194.5739792695554</v>
       </c>
       <c r="Y1" s="37">
         <f t="shared" si="0"/>
-        <v>251.67895475262128</v>
+        <v>3059.1035096599735</v>
       </c>
       <c r="Z1" s="37">
         <f t="shared" si="0"/>
-        <v>349.54800896254693</v>
+        <v>3947.5055297949793</v>
       </c>
       <c r="AA1" s="37">
         <f t="shared" si="0"/>
-        <v>489.37519127408848</v>
+        <v>5253.6774889295284</v>
       </c>
       <c r="AB1" s="37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>864.52953039041802</v>
       </c>
       <c r="AC1" s="37">
         <f t="shared" si="0"/>
-        <v>104.86540002957942</v>
+        <v>1307.8779841210726</v>
       </c>
       <c r="AD1" s="37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2615.7550559293181</v>
       </c>
       <c r="AE1" s="37">
         <f t="shared" si="0"/>
-        <v>230.6998907018133</v>
+        <v>3502.451963390628</v>
       </c>
       <c r="AF1" s="37">
         <f t="shared" si="0"/>
-        <v>321.57758579616183</v>
+        <v>4832.4964122697647</v>
       </c>
       <c r="AG1" s="37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5697.0259426601833</v>
       </c>
       <c r="AH1" s="37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>659.22447642386703</v>
       </c>
       <c r="AI1" s="37">
         <f t="shared" si="0"/>
-        <v>94.373374652137059</v>
+        <v>1393.8187647390264</v>
       </c>
       <c r="AJ1" s="37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2194.5739792695554</v>
       </c>
       <c r="AK1" s="37">
         <f t="shared" si="0"/>
-        <v>202.734454239505</v>
+        <v>3059.1035096599735</v>
       </c>
       <c r="AL1" s="37">
         <f t="shared" si="0"/>
-        <v>265.6566862796987</v>
+        <v>3947.5055297949793</v>
       </c>
       <c r="AM1" s="37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5253.6774889295284</v>
       </c>
       <c r="AN1" s="37">
         <f t="shared" si="0"/>
-        <v>1.236702611029326</v>
+        <v>18.795468862231637</v>
       </c>
       <c r="AO1" s="37">
         <f t="shared" si="0"/>
-        <v>55.796231914544869</v>
+        <v>847.12716321504331</v>
       </c>
       <c r="AP1" s="37">
         <f t="shared" si="0"/>
-        <v>1.2965430599500998</v>
+        <v>19.682236930093453</v>
       </c>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
@@ -7982,164 +7991,154 @@
         <v>1982</v>
       </c>
       <c r="B2" s="37">
-        <v>2057.1799999999998</v>
+        <v>8855.34</v>
       </c>
       <c r="C2" s="31">
-        <v>1646.04</v>
+        <v>7085.03</v>
       </c>
       <c r="D2" s="31">
-        <v>1234.1600000000001</v>
+        <v>5312.2</v>
       </c>
       <c r="E2">
-        <v>986.51</v>
+        <v>4246.62</v>
       </c>
       <c r="F2" s="37">
-        <f t="shared" ref="F2:J2" si="1">F1+F1*$A$5</f>
-        <v>877.10705670590517</v>
+        <v>3540.94</v>
       </c>
       <c r="G2" s="37">
+        <v>2833.7</v>
+      </c>
+      <c r="H2" s="37">
+        <v>2475.36</v>
+      </c>
+      <c r="I2" s="37">
+        <v>2122.0500000000002</v>
+      </c>
+      <c r="J2" s="37">
+        <v>1768.43</v>
+      </c>
+      <c r="K2" s="37">
+        <v>0</v>
+      </c>
+      <c r="L2" s="37">
+        <v>1684.9016954520282</v>
+      </c>
+      <c r="M2" s="37">
+        <v>1581.8039284229085</v>
+      </c>
+      <c r="N2" s="37">
+        <v>0</v>
+      </c>
+      <c r="O2" s="37">
+        <v>0</v>
+      </c>
+      <c r="P2" s="37">
+        <f>P3*$A$8</f>
+        <v>707.95269417989414</v>
+      </c>
+      <c r="Q2" s="37">
+        <f t="shared" ref="Q2:AP2" si="1">Q3*$A$8</f>
+        <v>353.97634708994707</v>
+      </c>
+      <c r="R2" s="37">
         <f t="shared" si="1"/>
-        <v>701.87741515028426</v>
-      </c>
-      <c r="H2" s="37">
+        <v>0</v>
+      </c>
+      <c r="S2" s="37">
         <f t="shared" si="1"/>
-        <v>613.18388932869777</v>
-      </c>
-      <c r="I2" s="37">
+        <v>0</v>
+      </c>
+      <c r="T2" s="37">
         <f t="shared" si="1"/>
-        <v>525.68892466686248</v>
-      </c>
-      <c r="J2" s="37">
+        <v>0</v>
+      </c>
+      <c r="U2" s="37">
         <f t="shared" si="1"/>
-        <v>437.95424777307699</v>
-      </c>
-      <c r="K2" s="37">
-        <f t="shared" ref="K2:U2" si="2">K1+K1*$A$5</f>
-        <v>0</v>
-      </c>
-      <c r="L2" s="37">
-        <f t="shared" si="2"/>
-        <v>349.2607219514905</v>
-      </c>
-      <c r="M2" s="37">
-        <f t="shared" si="2"/>
-        <v>298.2020165460907</v>
-      </c>
-      <c r="N2" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O2" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P2" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q2" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R2" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S2" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T2" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U2" s="37">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V2" s="37">
-        <f>V3*$A$11</f>
-        <v>950.73560804076317</v>
+        <f t="shared" si="1"/>
+        <v>2736.9438733316551</v>
       </c>
       <c r="W2" s="37">
-        <f t="shared" ref="W2:AP2" si="3">W3*$A$11</f>
-        <v>2112.6704480785352</v>
+        <f t="shared" si="1"/>
+        <v>5786.8053525281093</v>
       </c>
       <c r="X2" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>9111.3513256035094</v>
       </c>
       <c r="Y2" s="37">
-        <f t="shared" si="3"/>
-        <v>3802.7917370278424</v>
+        <f t="shared" si="1"/>
+        <v>12700.673151686546</v>
       </c>
       <c r="Z2" s="37">
-        <f t="shared" si="3"/>
-        <v>5281.5630988449311</v>
+        <f t="shared" si="1"/>
+        <v>16389.107900429954</v>
       </c>
       <c r="AA2" s="37">
-        <f t="shared" si="3"/>
-        <v>7394.3088944910714</v>
+        <f t="shared" si="1"/>
+        <v>21812.024477290055</v>
       </c>
       <c r="AB2" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3589.3218260830358</v>
       </c>
       <c r="AC2" s="37">
-        <f t="shared" si="3"/>
-        <v>1584.4839991670003</v>
+        <f t="shared" si="1"/>
+        <v>5429.9995884921118</v>
       </c>
       <c r="AD2" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>10859.995389277468</v>
       </c>
       <c r="AE2" s="37">
-        <f t="shared" si="3"/>
-        <v>3485.8045201133159</v>
+        <f t="shared" si="1"/>
+        <v>14541.350914095621</v>
       </c>
       <c r="AF2" s="37">
-        <f t="shared" si="3"/>
-        <v>4858.9385921480971</v>
+        <f t="shared" si="1"/>
+        <v>20063.380413616094</v>
       </c>
       <c r="AG2" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>23652.702239699131</v>
       </c>
       <c r="AH2" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2736.9438733316551</v>
       </c>
       <c r="AI2" s="37">
-        <f t="shared" si="3"/>
-        <v>1425.9527169259345</v>
+        <f t="shared" si="1"/>
+        <v>5786.8053525281093</v>
       </c>
       <c r="AJ2" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>9111.3513256035094</v>
       </c>
       <c r="AK2" s="37">
-        <f t="shared" si="3"/>
-        <v>3063.2553609840879</v>
+        <f t="shared" si="1"/>
+        <v>12700.673151686546</v>
       </c>
       <c r="AL2" s="37">
-        <f t="shared" si="3"/>
-        <v>4013.9909690248514</v>
+        <f t="shared" si="1"/>
+        <v>16389.107900429954</v>
       </c>
       <c r="AM2" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>21812.024477290055</v>
       </c>
       <c r="AN2" s="37">
-        <f t="shared" si="3"/>
-        <v>18.686196766057162</v>
+        <f t="shared" si="1"/>
+        <v>78.034334568312659</v>
       </c>
       <c r="AO2" s="37">
-        <f t="shared" si="3"/>
-        <v>843.0639339331193</v>
+        <f t="shared" si="1"/>
+        <v>3517.0713197297418</v>
       </c>
       <c r="AP2" s="37">
-        <f t="shared" si="3"/>
-        <v>19.590367577317991</v>
+        <f t="shared" si="1"/>
+        <v>81.715985534257698</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
@@ -8147,41 +8146,40 @@
         <v>1983</v>
       </c>
       <c r="B3" s="37">
-        <v>8855.34</v>
+        <v>23363.5</v>
       </c>
       <c r="C3" s="31">
-        <v>7085.03</v>
+        <v>18690.8</v>
       </c>
       <c r="D3" s="31">
-        <v>5312.2</v>
+        <v>14018.1</v>
       </c>
       <c r="E3" s="37">
-        <v>4246.62</v>
+        <v>11214.48</v>
       </c>
       <c r="F3" s="37">
-        <v>3540.94</v>
+        <v>9345.4</v>
       </c>
       <c r="G3" s="37">
-        <v>2833.7</v>
+        <v>7476.32</v>
       </c>
       <c r="H3" s="37">
-        <v>2475.36</v>
+        <v>6541.78</v>
       </c>
       <c r="I3" s="37">
-        <v>2122.0500000000002</v>
+        <v>5607.24</v>
       </c>
       <c r="J3" s="37">
-        <v>1768.43</v>
+        <v>4672.7</v>
       </c>
       <c r="K3" s="37">
         <v>0</v>
       </c>
       <c r="L3" s="37">
-        <v>1684.9016954520282</v>
+        <v>3738.16</v>
       </c>
       <c r="M3" s="37">
-        <f>M2+M2*A8</f>
-        <v>1581.8039284229085</v>
+        <v>2803.62</v>
       </c>
       <c r="N3" s="37">
         <v>0</v>
@@ -8190,10 +8188,10 @@
         <v>0</v>
       </c>
       <c r="P3" s="37">
-        <v>0</v>
+        <v>1869.08</v>
       </c>
       <c r="Q3" s="37">
-        <v>0</v>
+        <v>934.54</v>
       </c>
       <c r="R3" s="37">
         <v>0</v>
@@ -8208,67 +8206,67 @@
         <v>0</v>
       </c>
       <c r="V3" s="37">
-        <v>4092.413781176841</v>
+        <v>7225.86</v>
       </c>
       <c r="W3" s="37">
-        <v>9093.928515645699</v>
+        <v>15277.86</v>
       </c>
       <c r="X3" s="37">
-        <v>0</v>
+        <v>24055.06</v>
       </c>
       <c r="Y3" s="37">
-        <v>16369.006461879471</v>
+        <v>33531.300000000003</v>
       </c>
       <c r="Z3" s="37">
-        <v>22734.334791993333</v>
+        <v>43269.21</v>
       </c>
       <c r="AA3" s="37">
-        <v>31828.587639052981</v>
+        <v>57586.36</v>
       </c>
       <c r="AB3" s="37">
-        <v>0</v>
+        <v>9476.24</v>
       </c>
       <c r="AC3" s="37">
-        <v>6820.3653038807888</v>
+        <v>14335.85</v>
       </c>
       <c r="AD3" s="37">
-        <v>0</v>
+        <v>28671.69</v>
       </c>
       <c r="AE3" s="37">
-        <v>15004.544203406576</v>
+        <v>38390.910000000003</v>
       </c>
       <c r="AF3" s="37">
-        <v>20915.159891167455</v>
+        <v>52969.73</v>
       </c>
       <c r="AG3" s="37">
-        <v>0</v>
+        <v>62445.97</v>
       </c>
       <c r="AH3" s="37">
-        <v>0</v>
+        <v>7225.86</v>
       </c>
       <c r="AI3" s="37">
-        <v>6137.9720089373686</v>
+        <v>15277.86</v>
       </c>
       <c r="AJ3" s="37">
-        <v>0</v>
+        <v>24055.06</v>
       </c>
       <c r="AK3" s="37">
-        <v>13185.693633994648</v>
+        <v>33531.300000000003</v>
       </c>
       <c r="AL3" s="37">
-        <v>17278.107415171489</v>
+        <v>43269.21</v>
       </c>
       <c r="AM3" s="37">
-        <v>0</v>
+        <v>57586.36</v>
       </c>
       <c r="AN3">
-        <v>80.434190658730117</v>
+        <v>206.02</v>
       </c>
       <c r="AO3">
-        <v>3628.9441906473035</v>
+        <v>9285.49</v>
       </c>
       <c r="AP3">
-        <v>84.326167626088022</v>
+        <v>215.74</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.25">
@@ -8277,19 +8275,19 @@
       </c>
       <c r="B4" s="32">
         <f>B2/B1</f>
-        <v>15.109436512133499</v>
+        <v>4.3046014446961376</v>
       </c>
       <c r="C4" s="32">
-        <f t="shared" ref="C4:E4" si="4">C2/C1</f>
-        <v>15.110089843182008</v>
+        <f t="shared" ref="C4:E4" si="2">C2/C1</f>
+        <v>4.3042878666375053</v>
       </c>
       <c r="D4" s="32">
-        <f t="shared" si="4"/>
-        <v>15.110377157051152</v>
+        <f t="shared" si="2"/>
+        <v>4.3043041420885455</v>
       </c>
       <c r="E4" s="32">
-        <f t="shared" si="4"/>
-        <v>15.108868517266052</v>
+        <f t="shared" si="2"/>
+        <v>4.3046902717661251</v>
       </c>
       <c r="F4" s="32"/>
       <c r="G4" s="32"/>
@@ -8300,82 +8298,107 @@
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <f>AVERAGE(B4:E4)</f>
-        <v>15.109693007408179</v>
+        <v>4.3044709312970788</v>
       </c>
       <c r="L5" s="38"/>
       <c r="M5" s="38"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B7" s="32">
-        <f>B3/B2</f>
-        <v>4.3046014446961376</v>
+        <f>B2/B3</f>
+        <v>0.3790245468358765</v>
       </c>
       <c r="C7" s="32">
-        <f t="shared" ref="C7:E7" si="5">C3/C2</f>
-        <v>4.3042878666375053</v>
+        <f t="shared" ref="C7:J7" si="3">C2/C3</f>
+        <v>0.37906510154728529</v>
       </c>
       <c r="D7" s="32">
-        <f t="shared" si="5"/>
-        <v>4.3043041420885455</v>
+        <f t="shared" si="3"/>
+        <v>0.37895292514677448</v>
       </c>
       <c r="E7" s="32">
-        <f t="shared" si="5"/>
-        <v>4.3046902717661251</v>
+        <f t="shared" si="3"/>
+        <v>0.3786729299976459</v>
+      </c>
+      <c r="F7" s="32">
+        <f t="shared" si="3"/>
+        <v>0.3788965694352302</v>
+      </c>
+      <c r="G7" s="32">
+        <f t="shared" si="3"/>
+        <v>0.37902336978620499</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" si="3"/>
+        <v>0.37839242530320499</v>
+      </c>
+      <c r="I7" s="32">
+        <f t="shared" si="3"/>
+        <v>0.37844822051490579</v>
+      </c>
+      <c r="J7" s="32">
+        <f t="shared" si="3"/>
+        <v>0.3784599910116207</v>
       </c>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
-        <f>AVERAGE(B7:E7)</f>
-        <v>4.3044709312970788</v>
+        <f>AVERAGE(B7:J7)</f>
+        <v>0.37877067550874988</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B10" s="32">
-        <f>B2/B3</f>
+        <f>B1/B2</f>
         <v>0.23230954429756506</v>
       </c>
       <c r="C10" s="32">
-        <f t="shared" ref="C10:E10" si="6">C2/C3</f>
+        <f t="shared" ref="C10:J10" si="4">C1/C2</f>
         <v>0.23232646862469178</v>
       </c>
       <c r="D10" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0.23232559015097326</v>
       </c>
       <c r="E10" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0.23230475060165498</v>
+      </c>
+      <c r="F10" s="32">
+        <f t="shared" si="4"/>
+        <v>0.24770458033909221</v>
+      </c>
+      <c r="G10" s="32">
+        <f t="shared" si="4"/>
+        <v>0.24768938672064239</v>
+      </c>
+      <c r="H10" s="32">
+        <f t="shared" si="4"/>
+        <v>0.24771503511759815</v>
+      </c>
+      <c r="I10" s="32">
+        <f t="shared" si="4"/>
+        <v>0.24772692663549983</v>
+      </c>
+      <c r="J10" s="32">
+        <f t="shared" si="4"/>
+        <v>0.24765144663519448</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
-        <f>AVERAGE(B10:E10)</f>
-        <v>0.2323165884187213</v>
+        <f>AVERAGE(B10:J10)</f>
+        <v>0.24086152545810136</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="B13" s="32">
-        <f>B1/B2</f>
-        <v>6.6183805014631683E-2</v>
-      </c>
-      <c r="C13" s="32">
-        <f t="shared" ref="C13:E13" si="7">C1/C2</f>
-        <v>6.6180943354960997E-2</v>
-      </c>
-      <c r="D13" s="32">
-        <f t="shared" si="7"/>
-        <v>6.6179684967913391E-2</v>
-      </c>
-      <c r="E13" s="32">
-        <f t="shared" si="7"/>
-        <v>6.6186293093835849E-2</v>
-      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A14" s="33">
-        <f>AVERAGE(B13:E13)</f>
-        <v>6.618268160783547E-2</v>
-      </c>
+      <c r="A14" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
